--- a/Documents/Phissing Email System Gantt chart.xlsx
+++ b/Documents/Phissing Email System Gantt chart.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{70EE82E3-3C14-4A92-BC4E-930F54CDDDB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A648C6DB-798B-4A14-948B-EAE80BC8228A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="415" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="40">
   <si>
     <t>Project start date:</t>
   </si>
@@ -170,31 +170,7 @@
     <t>Future - Maintenance</t>
   </si>
   <si>
-    <t xml:space="preserve">Mazen </t>
-  </si>
-  <si>
-    <t>Omar</t>
-  </si>
-  <si>
-    <t>Hassan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aml </t>
-  </si>
-  <si>
-    <t>Ahmed</t>
-  </si>
-  <si>
-    <t>Aml &amp; Hassan</t>
-  </si>
-  <si>
-    <t>All team</t>
-  </si>
-  <si>
-    <t>Aml</t>
-  </si>
-  <si>
-    <t>Mazen &amp; Hassan</t>
+    <t>Column1</t>
   </si>
 </sst>
 </file>
@@ -204,9 +180,9 @@
   <numFmts count="3">
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="d"/>
-    <numFmt numFmtId="168" formatCode="m/d;@"/>
+    <numFmt numFmtId="165" formatCode="m/d;@"/>
   </numFmts>
-  <fonts count="34" x14ac:knownFonts="1">
+  <fonts count="35" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="8" tint="-0.499984740745262"/>
@@ -450,6 +426,12 @@
       <color theme="6" tint="-0.249977111117893"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="11">
@@ -1059,17 +1041,17 @@
     <xf numFmtId="0" fontId="17" fillId="2" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="3" fillId="0" borderId="0" xfId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="13">
@@ -1747,8 +1729,8 @@
   </autoFilter>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{97DEBD95-3A3B-4C26-817D-34A0DA6472E7}" name="Milestone description"/>
-    <tableColumn id="3" xr3:uid="{76EB9444-C31F-4CC3-88B2-0202B5893122}" name="Assigned to"/>
-    <tableColumn id="4" xr3:uid="{52A1E4A6-5AE1-47AB-95DD-0B2C1394989A}" name="Progress"/>
+    <tableColumn id="3" xr3:uid="{76EB9444-C31F-4CC3-88B2-0202B5893122}" name="Progress"/>
+    <tableColumn id="4" xr3:uid="{52A1E4A6-5AE1-47AB-95DD-0B2C1394989A}" name="Column1"/>
     <tableColumn id="5" xr3:uid="{0671DF77-A989-41EA-819F-AF0A8A45AB0F}" name="Start"/>
     <tableColumn id="6" xr3:uid="{B1E97C69-5901-4994-8267-A58A1A9D9898}" name="Days"/>
   </tableColumns>
@@ -2148,8 +2130,8 @@
   <cols>
     <col min="1" max="1" width="4.6640625" style="9" customWidth="1"/>
     <col min="2" max="2" width="25.6640625" customWidth="1"/>
-    <col min="3" max="3" width="18.6640625" customWidth="1"/>
-    <col min="4" max="4" width="13.6640625" customWidth="1"/>
+    <col min="3" max="3" width="19.109375" customWidth="1"/>
+    <col min="4" max="4" width="13.6640625" hidden="1" customWidth="1"/>
     <col min="5" max="5" width="13.6640625" style="2" customWidth="1"/>
     <col min="6" max="6" width="13.6640625" customWidth="1"/>
     <col min="7" max="7" width="2.6640625" customWidth="1"/>
@@ -2319,18 +2301,18 @@
       <c r="K5" s="35"/>
       <c r="L5" s="35"/>
       <c r="M5" s="36"/>
-      <c r="O5" s="107" t="s">
+      <c r="O5" s="109" t="s">
         <v>1</v>
       </c>
-      <c r="P5" s="107"/>
-      <c r="Q5" s="107"/>
-      <c r="R5" s="107"/>
-      <c r="S5" s="107"/>
-      <c r="T5" s="107"/>
-      <c r="U5" s="108">
+      <c r="P5" s="109"/>
+      <c r="Q5" s="109"/>
+      <c r="R5" s="109"/>
+      <c r="S5" s="109"/>
+      <c r="T5" s="109"/>
+      <c r="U5" s="110">
         <v>0</v>
       </c>
-      <c r="V5" s="108"/>
+      <c r="V5" s="110"/>
     </row>
     <row r="6" spans="1:63" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="10"/>
@@ -2340,10 +2322,7 @@
       <c r="C6" s="52">
         <v>1</v>
       </c>
-      <c r="D6" s="52">
-        <f>Milestone_Marker</f>
-        <v>1</v>
-      </c>
+      <c r="D6" s="52"/>
       <c r="H6" s="80" t="str">
         <f ca="1">TEXT(H7,"mmmm")</f>
         <v>October</v>
@@ -2659,10 +2638,10 @@
         <v>3</v>
       </c>
       <c r="C8" s="103" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D8" s="103" t="s">
-        <v>5</v>
+        <v>39</v>
       </c>
       <c r="E8" s="103" t="s">
         <v>6</v>
@@ -3199,13 +3178,11 @@
       <c r="B11" s="53" t="s">
         <v>29</v>
       </c>
-      <c r="C11" s="17" t="s">
-        <v>45</v>
-      </c>
-      <c r="D11" s="94">
+      <c r="C11" s="94">
         <v>1</v>
       </c>
-      <c r="E11" s="109">
+      <c r="D11" s="94"/>
+      <c r="E11" s="107">
         <v>45931</v>
       </c>
       <c r="F11" s="16">
@@ -3442,13 +3419,11 @@
       <c r="B12" s="53" t="s">
         <v>30</v>
       </c>
-      <c r="C12" s="17" t="s">
-        <v>39</v>
-      </c>
-      <c r="D12" s="94">
+      <c r="C12" s="94">
         <v>1</v>
       </c>
-      <c r="E12" s="109">
+      <c r="D12" s="94"/>
+      <c r="E12" s="107">
         <v>45937</v>
       </c>
       <c r="F12" s="16">
@@ -3685,13 +3660,11 @@
       <c r="B13" s="53" t="s">
         <v>31</v>
       </c>
-      <c r="C13" s="17" t="s">
-        <v>40</v>
-      </c>
-      <c r="D13" s="94">
+      <c r="C13" s="94">
         <v>1</v>
       </c>
-      <c r="E13" s="109">
+      <c r="D13" s="94"/>
+      <c r="E13" s="107">
         <v>45940</v>
       </c>
       <c r="F13" s="16">
@@ -3928,13 +3901,11 @@
       <c r="B14" s="53" t="s">
         <v>32</v>
       </c>
-      <c r="C14" s="17" t="s">
-        <v>41</v>
-      </c>
-      <c r="D14" s="94">
+      <c r="C14" s="94">
         <v>1</v>
       </c>
-      <c r="E14" s="109">
+      <c r="D14" s="94"/>
+      <c r="E14" s="107">
         <v>45947</v>
       </c>
       <c r="F14" s="16">
@@ -4171,13 +4142,11 @@
       <c r="B15" s="53" t="s">
         <v>33</v>
       </c>
-      <c r="C15" s="17" t="s">
-        <v>42</v>
-      </c>
-      <c r="D15" s="94">
+      <c r="C15" s="94">
         <v>1</v>
       </c>
-      <c r="E15" s="109">
+      <c r="D15" s="94"/>
+      <c r="E15" s="107">
         <v>45955</v>
       </c>
       <c r="F15" s="16">
@@ -4411,16 +4380,14 @@
     </row>
     <row r="16" spans="1:63" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="10"/>
-      <c r="B16" s="110" t="s">
+      <c r="B16" s="108" t="s">
         <v>34</v>
       </c>
-      <c r="C16" s="17" t="s">
-        <v>47</v>
-      </c>
-      <c r="D16" s="94">
+      <c r="C16" s="94">
         <v>1</v>
       </c>
-      <c r="E16" s="109">
+      <c r="D16" s="94"/>
+      <c r="E16" s="107">
         <v>45961</v>
       </c>
       <c r="F16" s="16">
@@ -4657,13 +4624,11 @@
       <c r="B17" s="53" t="s">
         <v>35</v>
       </c>
-      <c r="C17" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="D17" s="94">
+      <c r="C17" s="94">
         <v>1</v>
       </c>
-      <c r="E17" s="109">
+      <c r="D17" s="94"/>
+      <c r="E17" s="107">
         <v>45966</v>
       </c>
       <c r="F17" s="16">
@@ -4900,13 +4865,11 @@
       <c r="B18" s="53" t="s">
         <v>36</v>
       </c>
-      <c r="C18" s="17" t="s">
-        <v>44</v>
-      </c>
-      <c r="D18" s="94">
+      <c r="C18" s="94">
         <v>1</v>
       </c>
-      <c r="E18" s="109">
+      <c r="D18" s="94"/>
+      <c r="E18" s="107">
         <v>45973</v>
       </c>
       <c r="F18" s="16">
@@ -5143,13 +5106,11 @@
       <c r="B19" s="53" t="s">
         <v>37</v>
       </c>
-      <c r="C19" s="17" t="s">
-        <v>45</v>
-      </c>
-      <c r="D19" s="94">
+      <c r="C19" s="94">
         <v>1</v>
       </c>
-      <c r="E19" s="109">
+      <c r="D19" s="94"/>
+      <c r="E19" s="107">
         <v>45978</v>
       </c>
       <c r="F19" s="16">
@@ -5386,13 +5347,11 @@
       <c r="B20" s="53" t="s">
         <v>38</v>
       </c>
-      <c r="C20" s="17" t="s">
-        <v>46</v>
-      </c>
-      <c r="D20" s="94">
+      <c r="C20" s="94">
         <v>0</v>
       </c>
-      <c r="E20" s="109"/>
+      <c r="D20" s="94"/>
+      <c r="E20" s="107"/>
       <c r="F20" s="16"/>
       <c r="G20" s="31"/>
       <c r="H20" s="30" t="str">
@@ -5625,7 +5584,7 @@
       <c r="B21" s="53"/>
       <c r="C21" s="17"/>
       <c r="D21" s="94"/>
-      <c r="E21" s="109"/>
+      <c r="E21" s="107"/>
       <c r="F21" s="16"/>
       <c r="G21" s="31"/>
       <c r="H21" s="30"/>
@@ -5690,7 +5649,7 @@
       <c r="B22" s="44"/>
       <c r="C22" s="17"/>
       <c r="D22" s="94"/>
-      <c r="E22" s="109"/>
+      <c r="E22" s="107"/>
       <c r="F22" s="16"/>
       <c r="G22" s="31"/>
       <c r="H22" s="30"/>
@@ -5755,7 +5714,7 @@
       <c r="B23" s="53"/>
       <c r="C23" s="17"/>
       <c r="D23" s="94"/>
-      <c r="E23" s="109"/>
+      <c r="E23" s="107"/>
       <c r="F23" s="16"/>
       <c r="G23" s="31"/>
       <c r="H23" s="30"/>
@@ -5820,7 +5779,7 @@
       <c r="B24" s="53"/>
       <c r="C24" s="17"/>
       <c r="D24" s="94"/>
-      <c r="E24" s="109"/>
+      <c r="E24" s="107"/>
       <c r="F24" s="16"/>
       <c r="G24" s="31"/>
       <c r="H24" s="30"/>
@@ -5885,7 +5844,7 @@
       <c r="B25" s="53"/>
       <c r="C25" s="17"/>
       <c r="D25" s="94"/>
-      <c r="E25" s="109"/>
+      <c r="E25" s="107"/>
       <c r="F25" s="16"/>
       <c r="G25" s="31"/>
       <c r="H25" s="30"/>
@@ -5950,7 +5909,7 @@
       <c r="B26" s="53"/>
       <c r="C26" s="17"/>
       <c r="D26" s="94"/>
-      <c r="E26" s="109"/>
+      <c r="E26" s="107"/>
       <c r="F26" s="16"/>
       <c r="G26" s="31"/>
       <c r="H26" s="30"/>
@@ -6015,7 +5974,7 @@
       <c r="B27" s="53"/>
       <c r="C27" s="17"/>
       <c r="D27" s="94"/>
-      <c r="E27" s="109"/>
+      <c r="E27" s="107"/>
       <c r="F27" s="16"/>
       <c r="G27" s="31"/>
       <c r="H27" s="30"/>
@@ -6080,7 +6039,7 @@
       <c r="B28" s="44"/>
       <c r="C28" s="17"/>
       <c r="D28" s="94"/>
-      <c r="E28" s="109"/>
+      <c r="E28" s="107"/>
       <c r="F28" s="16"/>
       <c r="G28" s="31"/>
       <c r="H28" s="30"/>
@@ -6145,7 +6104,7 @@
       <c r="B29" s="53"/>
       <c r="C29" s="17"/>
       <c r="D29" s="94"/>
-      <c r="E29" s="109"/>
+      <c r="E29" s="107"/>
       <c r="F29" s="16"/>
       <c r="G29" s="31"/>
       <c r="H29" s="30"/>
@@ -6210,7 +6169,7 @@
       <c r="B30" s="53"/>
       <c r="C30" s="17"/>
       <c r="D30" s="94"/>
-      <c r="E30" s="109"/>
+      <c r="E30" s="107"/>
       <c r="F30" s="16"/>
       <c r="G30" s="31"/>
       <c r="H30" s="30"/>
@@ -6275,7 +6234,7 @@
       <c r="B31" s="53"/>
       <c r="C31" s="17"/>
       <c r="D31" s="94"/>
-      <c r="E31" s="109"/>
+      <c r="E31" s="107"/>
       <c r="F31" s="16"/>
       <c r="G31" s="31"/>
       <c r="H31" s="30"/>
@@ -6778,7 +6737,8 @@
     <mergeCell ref="O5:T5"/>
     <mergeCell ref="U5:V5"/>
   </mergeCells>
-  <conditionalFormatting sqref="D8:D34">
+  <phoneticPr fontId="34" type="noConversion"/>
+  <conditionalFormatting sqref="D8:D34 C11:C20 C8">
     <cfRule type="dataBar" priority="4">
       <dataBar>
         <cfvo type="num" val="0"/>
@@ -6892,7 +6852,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>D8:D34</xm:sqref>
+          <xm:sqref>D8:D34 C11:C20 C8</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="iconSet" priority="3" id="{541F8E9A-B35A-48E2-8231-2B95FF5B4F9D}">
@@ -7091,7 +7051,7 @@
       </c>
       <c r="C5" s="51">
         <f ca="1">IFERROR(IF(MIN(Milestones3[Start])=0,TODAY(),MIN(Milestones3[Start])),TODAY())</f>
-        <v>45988</v>
+        <v>45989</v>
       </c>
       <c r="E5" s="67"/>
       <c r="H5" s="37"/>
@@ -7100,18 +7060,18 @@
       <c r="K5" s="38"/>
       <c r="L5" s="38"/>
       <c r="M5" s="39"/>
-      <c r="O5" s="107" t="s">
+      <c r="O5" s="109" t="s">
         <v>1</v>
       </c>
-      <c r="P5" s="107"/>
-      <c r="Q5" s="107"/>
-      <c r="R5" s="107"/>
-      <c r="S5" s="107"/>
-      <c r="T5" s="107"/>
-      <c r="U5" s="108">
+      <c r="P5" s="109"/>
+      <c r="Q5" s="109"/>
+      <c r="R5" s="109"/>
+      <c r="S5" s="109"/>
+      <c r="T5" s="109"/>
+      <c r="U5" s="110">
         <v>13</v>
       </c>
-      <c r="V5" s="108"/>
+      <c r="V5" s="110"/>
     </row>
     <row r="6" spans="1:63" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="10"/>
@@ -7157,7 +7117,7 @@
       <c r="AB6" s="27"/>
       <c r="AC6" s="27" t="str">
         <f ca="1">IF(OR(TEXT(AC7,"mmmm")=V6,TEXT(AC7,"mmmm")=O6,TEXT(AC7,"mmmm")=H6),"",TEXT(AC7,"mmmm"))</f>
-        <v/>
+        <v>January</v>
       </c>
       <c r="AD6" s="27"/>
       <c r="AE6" s="27"/>
@@ -7167,7 +7127,7 @@
       <c r="AI6" s="27"/>
       <c r="AJ6" s="81" t="str">
         <f ca="1">IF(OR(TEXT(AJ7,"mmmm")=AC6,TEXT(AJ7,"mmmm")=V6,TEXT(AJ7,"mmmm")=O6,TEXT(AJ7,"mmmm")=H6),"",TEXT(AJ7,"mmmm"))</f>
-        <v>January</v>
+        <v/>
       </c>
       <c r="AK6" s="81"/>
       <c r="AL6" s="81"/>
@@ -7211,227 +7171,227 @@
       <c r="B7" s="23"/>
       <c r="H7" s="55">
         <f ca="1">IFERROR(Project_Start+Scrolling_Increment,TODAY())</f>
-        <v>46001</v>
+        <v>46002</v>
       </c>
       <c r="I7" s="56">
         <f ca="1">H7+1</f>
-        <v>46002</v>
+        <v>46003</v>
       </c>
       <c r="J7" s="56">
         <f t="shared" ref="J7:AW7" ca="1" si="0">I7+1</f>
-        <v>46003</v>
+        <v>46004</v>
       </c>
       <c r="K7" s="56">
         <f ca="1">J7+1</f>
-        <v>46004</v>
+        <v>46005</v>
       </c>
       <c r="L7" s="56">
         <f t="shared" ca="1" si="0"/>
-        <v>46005</v>
+        <v>46006</v>
       </c>
       <c r="M7" s="56">
         <f t="shared" ca="1" si="0"/>
-        <v>46006</v>
+        <v>46007</v>
       </c>
       <c r="N7" s="56">
         <f t="shared" ca="1" si="0"/>
-        <v>46007</v>
+        <v>46008</v>
       </c>
       <c r="O7" s="56">
         <f ca="1">N7+1</f>
-        <v>46008</v>
+        <v>46009</v>
       </c>
       <c r="P7" s="56">
         <f ca="1">O7+1</f>
-        <v>46009</v>
+        <v>46010</v>
       </c>
       <c r="Q7" s="56">
         <f t="shared" ca="1" si="0"/>
-        <v>46010</v>
+        <v>46011</v>
       </c>
       <c r="R7" s="56">
         <f t="shared" ca="1" si="0"/>
-        <v>46011</v>
+        <v>46012</v>
       </c>
       <c r="S7" s="56">
         <f t="shared" ca="1" si="0"/>
-        <v>46012</v>
+        <v>46013</v>
       </c>
       <c r="T7" s="56">
         <f t="shared" ca="1" si="0"/>
-        <v>46013</v>
+        <v>46014</v>
       </c>
       <c r="U7" s="56">
         <f t="shared" ca="1" si="0"/>
-        <v>46014</v>
+        <v>46015</v>
       </c>
       <c r="V7" s="56">
         <f ca="1">U7+1</f>
-        <v>46015</v>
+        <v>46016</v>
       </c>
       <c r="W7" s="56">
         <f ca="1">V7+1</f>
-        <v>46016</v>
+        <v>46017</v>
       </c>
       <c r="X7" s="56">
         <f t="shared" ca="1" si="0"/>
-        <v>46017</v>
+        <v>46018</v>
       </c>
       <c r="Y7" s="56">
         <f t="shared" ca="1" si="0"/>
-        <v>46018</v>
+        <v>46019</v>
       </c>
       <c r="Z7" s="56">
         <f t="shared" ca="1" si="0"/>
-        <v>46019</v>
+        <v>46020</v>
       </c>
       <c r="AA7" s="56">
         <f t="shared" ca="1" si="0"/>
-        <v>46020</v>
+        <v>46021</v>
       </c>
       <c r="AB7" s="56">
         <f t="shared" ca="1" si="0"/>
-        <v>46021</v>
+        <v>46022</v>
       </c>
       <c r="AC7" s="56">
         <f ca="1">AB7+1</f>
-        <v>46022</v>
+        <v>46023</v>
       </c>
       <c r="AD7" s="56">
         <f ca="1">AC7+1</f>
-        <v>46023</v>
+        <v>46024</v>
       </c>
       <c r="AE7" s="56">
         <f t="shared" ca="1" si="0"/>
-        <v>46024</v>
+        <v>46025</v>
       </c>
       <c r="AF7" s="56">
         <f t="shared" ca="1" si="0"/>
-        <v>46025</v>
+        <v>46026</v>
       </c>
       <c r="AG7" s="56">
         <f t="shared" ca="1" si="0"/>
-        <v>46026</v>
+        <v>46027</v>
       </c>
       <c r="AH7" s="56">
         <f t="shared" ca="1" si="0"/>
-        <v>46027</v>
+        <v>46028</v>
       </c>
       <c r="AI7" s="56">
         <f t="shared" ca="1" si="0"/>
-        <v>46028</v>
+        <v>46029</v>
       </c>
       <c r="AJ7" s="56">
         <f ca="1">AI7+1</f>
-        <v>46029</v>
+        <v>46030</v>
       </c>
       <c r="AK7" s="56">
         <f ca="1">AJ7+1</f>
-        <v>46030</v>
+        <v>46031</v>
       </c>
       <c r="AL7" s="56">
         <f t="shared" ca="1" si="0"/>
-        <v>46031</v>
+        <v>46032</v>
       </c>
       <c r="AM7" s="56">
         <f t="shared" ca="1" si="0"/>
-        <v>46032</v>
+        <v>46033</v>
       </c>
       <c r="AN7" s="56">
         <f t="shared" ca="1" si="0"/>
-        <v>46033</v>
+        <v>46034</v>
       </c>
       <c r="AO7" s="56">
         <f t="shared" ca="1" si="0"/>
-        <v>46034</v>
+        <v>46035</v>
       </c>
       <c r="AP7" s="56">
         <f t="shared" ca="1" si="0"/>
-        <v>46035</v>
+        <v>46036</v>
       </c>
       <c r="AQ7" s="56">
         <f ca="1">AP7+1</f>
-        <v>46036</v>
+        <v>46037</v>
       </c>
       <c r="AR7" s="56">
         <f ca="1">AQ7+1</f>
-        <v>46037</v>
+        <v>46038</v>
       </c>
       <c r="AS7" s="56">
         <f t="shared" ca="1" si="0"/>
-        <v>46038</v>
+        <v>46039</v>
       </c>
       <c r="AT7" s="56">
         <f t="shared" ca="1" si="0"/>
-        <v>46039</v>
+        <v>46040</v>
       </c>
       <c r="AU7" s="56">
         <f t="shared" ca="1" si="0"/>
-        <v>46040</v>
+        <v>46041</v>
       </c>
       <c r="AV7" s="56">
         <f t="shared" ca="1" si="0"/>
-        <v>46041</v>
+        <v>46042</v>
       </c>
       <c r="AW7" s="56">
         <f t="shared" ca="1" si="0"/>
-        <v>46042</v>
+        <v>46043</v>
       </c>
       <c r="AX7" s="56">
         <f ca="1">AW7+1</f>
-        <v>46043</v>
+        <v>46044</v>
       </c>
       <c r="AY7" s="56">
         <f ca="1">AX7+1</f>
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="AZ7" s="56">
         <f t="shared" ref="AZ7:BD7" ca="1" si="1">AY7+1</f>
-        <v>46045</v>
+        <v>46046</v>
       </c>
       <c r="BA7" s="56">
         <f t="shared" ca="1" si="1"/>
-        <v>46046</v>
+        <v>46047</v>
       </c>
       <c r="BB7" s="56">
         <f t="shared" ca="1" si="1"/>
-        <v>46047</v>
+        <v>46048</v>
       </c>
       <c r="BC7" s="56">
         <f t="shared" ca="1" si="1"/>
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="BD7" s="56">
         <f t="shared" ca="1" si="1"/>
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="BE7" s="56">
         <f ca="1">BD7+1</f>
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="BF7" s="56">
         <f ca="1">BE7+1</f>
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="BG7" s="56">
         <f t="shared" ref="BG7:BK7" ca="1" si="2">BF7+1</f>
-        <v>46052</v>
+        <v>46053</v>
       </c>
       <c r="BH7" s="56">
         <f t="shared" ca="1" si="2"/>
-        <v>46053</v>
+        <v>46054</v>
       </c>
       <c r="BI7" s="56">
         <f t="shared" ca="1" si="2"/>
-        <v>46054</v>
+        <v>46055</v>
       </c>
       <c r="BJ7" s="56">
         <f t="shared" ca="1" si="2"/>
-        <v>46055</v>
+        <v>46056</v>
       </c>
       <c r="BK7" s="70">
         <f t="shared" ca="1" si="2"/>
-        <v>46056</v>
+        <v>46057</v>
       </c>
     </row>
     <row r="8" spans="1:63" ht="31.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -7454,15 +7414,15 @@
       <c r="G8" s="72"/>
       <c r="H8" s="57" t="str">
         <f ca="1">LEFT(TEXT(H7,"ddd"),1)</f>
-        <v>W</v>
+        <v>T</v>
       </c>
       <c r="I8" s="54" t="str">
         <f ca="1">LEFT(TEXT(I7,"ddd"),1)</f>
-        <v>T</v>
+        <v>F</v>
       </c>
       <c r="J8" s="54" t="str">
         <f ca="1">LEFT(TEXT(J7,"ddd"),1)</f>
-        <v>F</v>
+        <v>S</v>
       </c>
       <c r="K8" s="54" t="str">
         <f t="shared" ref="K8:BK8" ca="1" si="3">LEFT(TEXT(K7,"ddd"),1)</f>
@@ -7470,27 +7430,27 @@
       </c>
       <c r="L8" s="54" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>S</v>
+        <v>M</v>
       </c>
       <c r="M8" s="54" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>M</v>
+        <v>T</v>
       </c>
       <c r="N8" s="54" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>T</v>
+        <v>W</v>
       </c>
       <c r="O8" s="54" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>W</v>
+        <v>T</v>
       </c>
       <c r="P8" s="54" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>T</v>
+        <v>F</v>
       </c>
       <c r="Q8" s="54" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>F</v>
+        <v>S</v>
       </c>
       <c r="R8" s="54" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -7498,27 +7458,27 @@
       </c>
       <c r="S8" s="54" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>S</v>
+        <v>M</v>
       </c>
       <c r="T8" s="54" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>M</v>
+        <v>T</v>
       </c>
       <c r="U8" s="54" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>T</v>
+        <v>W</v>
       </c>
       <c r="V8" s="54" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>W</v>
+        <v>T</v>
       </c>
       <c r="W8" s="54" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>T</v>
+        <v>F</v>
       </c>
       <c r="X8" s="54" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>F</v>
+        <v>S</v>
       </c>
       <c r="Y8" s="54" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -7526,27 +7486,27 @@
       </c>
       <c r="Z8" s="54" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>S</v>
+        <v>M</v>
       </c>
       <c r="AA8" s="54" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>M</v>
+        <v>T</v>
       </c>
       <c r="AB8" s="54" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>T</v>
+        <v>W</v>
       </c>
       <c r="AC8" s="54" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>W</v>
+        <v>T</v>
       </c>
       <c r="AD8" s="54" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>T</v>
+        <v>F</v>
       </c>
       <c r="AE8" s="54" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>F</v>
+        <v>S</v>
       </c>
       <c r="AF8" s="54" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -7554,27 +7514,27 @@
       </c>
       <c r="AG8" s="54" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>S</v>
+        <v>M</v>
       </c>
       <c r="AH8" s="54" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>M</v>
+        <v>T</v>
       </c>
       <c r="AI8" s="54" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>T</v>
+        <v>W</v>
       </c>
       <c r="AJ8" s="54" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>W</v>
+        <v>T</v>
       </c>
       <c r="AK8" s="54" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>T</v>
+        <v>F</v>
       </c>
       <c r="AL8" s="54" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>F</v>
+        <v>S</v>
       </c>
       <c r="AM8" s="54" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -7582,27 +7542,27 @@
       </c>
       <c r="AN8" s="54" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>S</v>
+        <v>M</v>
       </c>
       <c r="AO8" s="54" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>M</v>
+        <v>T</v>
       </c>
       <c r="AP8" s="54" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>T</v>
+        <v>W</v>
       </c>
       <c r="AQ8" s="54" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>W</v>
+        <v>T</v>
       </c>
       <c r="AR8" s="54" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>T</v>
+        <v>F</v>
       </c>
       <c r="AS8" s="54" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>F</v>
+        <v>S</v>
       </c>
       <c r="AT8" s="54" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -7610,27 +7570,27 @@
       </c>
       <c r="AU8" s="54" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>S</v>
+        <v>M</v>
       </c>
       <c r="AV8" s="54" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>M</v>
+        <v>T</v>
       </c>
       <c r="AW8" s="54" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>T</v>
+        <v>W</v>
       </c>
       <c r="AX8" s="54" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>W</v>
+        <v>T</v>
       </c>
       <c r="AY8" s="54" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>T</v>
+        <v>F</v>
       </c>
       <c r="AZ8" s="54" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>F</v>
+        <v>S</v>
       </c>
       <c r="BA8" s="54" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -7638,27 +7598,27 @@
       </c>
       <c r="BB8" s="54" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>S</v>
+        <v>M</v>
       </c>
       <c r="BC8" s="54" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>M</v>
+        <v>T</v>
       </c>
       <c r="BD8" s="54" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>T</v>
+        <v>W</v>
       </c>
       <c r="BE8" s="54" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>W</v>
+        <v>T</v>
       </c>
       <c r="BF8" s="54" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>T</v>
+        <v>F</v>
       </c>
       <c r="BG8" s="54" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>F</v>
+        <v>S</v>
       </c>
       <c r="BH8" s="54" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -7666,15 +7626,15 @@
       </c>
       <c r="BI8" s="54" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>S</v>
+        <v>M</v>
       </c>
       <c r="BJ8" s="54" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>M</v>
+        <v>T</v>
       </c>
       <c r="BK8" s="71" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>T</v>
+        <v>W</v>
       </c>
     </row>
     <row r="9" spans="1:63" ht="30" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -7986,7 +7946,7 @@
       </c>
       <c r="E11" s="46">
         <f ca="1">TODAY()</f>
-        <v>45991</v>
+        <v>45992</v>
       </c>
       <c r="F11" s="16">
         <v>3</v>
@@ -8226,7 +8186,7 @@
       <c r="D12" s="48"/>
       <c r="E12" s="46">
         <f ca="1">TODAY()+5</f>
-        <v>45996</v>
+        <v>45997</v>
       </c>
       <c r="F12" s="16">
         <v>1</v>
@@ -8468,7 +8428,7 @@
       </c>
       <c r="E13" s="46">
         <f ca="1">TODAY()-3</f>
-        <v>45988</v>
+        <v>45989</v>
       </c>
       <c r="F13" s="16">
         <v>10</v>
@@ -8708,7 +8668,7 @@
       <c r="D14" s="48"/>
       <c r="E14" s="46">
         <f ca="1">TODAY()+20</f>
-        <v>46011</v>
+        <v>46012</v>
       </c>
       <c r="F14" s="16">
         <v>1</v>
@@ -8950,7 +8910,7 @@
       </c>
       <c r="E15" s="46">
         <f ca="1">TODAY()+6</f>
-        <v>45997</v>
+        <v>45998</v>
       </c>
       <c r="F15" s="16">
         <v>6</v>
@@ -9427,7 +9387,7 @@
       </c>
       <c r="E17" s="46">
         <f ca="1">TODAY()+6</f>
-        <v>45997</v>
+        <v>45998</v>
       </c>
       <c r="F17" s="16">
         <v>13</v>
@@ -9669,7 +9629,7 @@
       </c>
       <c r="E18" s="46">
         <f ca="1">TODAY()+7</f>
-        <v>45998</v>
+        <v>45999</v>
       </c>
       <c r="F18" s="16">
         <v>9</v>
@@ -9911,7 +9871,7 @@
       </c>
       <c r="E19" s="46">
         <f ca="1">TODAY()+15</f>
-        <v>46006</v>
+        <v>46007</v>
       </c>
       <c r="F19" s="16">
         <v>11</v>
@@ -10151,7 +10111,7 @@
       <c r="D20" s="48"/>
       <c r="E20" s="46">
         <f ca="1">TODAY()+24</f>
-        <v>46015</v>
+        <v>46016</v>
       </c>
       <c r="F20" s="16">
         <v>1</v>
@@ -10391,7 +10351,7 @@
       <c r="D21" s="93"/>
       <c r="E21" s="46">
         <f ca="1">TODAY()+25</f>
-        <v>46016</v>
+        <v>46017</v>
       </c>
       <c r="F21" s="16">
         <v>24</v>
@@ -10866,7 +10826,7 @@
       <c r="D23" s="93"/>
       <c r="E23" s="46">
         <f ca="1">TODAY()+15</f>
-        <v>46006</v>
+        <v>46007</v>
       </c>
       <c r="F23" s="16">
         <v>4</v>
@@ -11106,7 +11066,7 @@
       <c r="D24" s="48"/>
       <c r="E24" s="46">
         <f ca="1">TODAY()+19</f>
-        <v>46010</v>
+        <v>46011</v>
       </c>
       <c r="F24" s="16">
         <v>14</v>
@@ -11346,7 +11306,7 @@
       <c r="D25" s="93"/>
       <c r="E25" s="46">
         <f ca="1">TODAY()+35</f>
-        <v>46026</v>
+        <v>46027</v>
       </c>
       <c r="F25" s="16">
         <v>6</v>
@@ -11586,7 +11546,7 @@
       <c r="D26" s="48"/>
       <c r="E26" s="46">
         <f ca="1">TODAY()+48</f>
-        <v>46039</v>
+        <v>46040</v>
       </c>
       <c r="F26" s="16">
         <v>3</v>
@@ -11826,7 +11786,7 @@
       <c r="D27" s="93"/>
       <c r="E27" s="46">
         <f ca="1">TODAY()+40</f>
-        <v>46031</v>
+        <v>46032</v>
       </c>
       <c r="F27" s="16">
         <v>19</v>
@@ -12301,7 +12261,7 @@
       <c r="D29" s="93"/>
       <c r="E29" s="46">
         <f ca="1">TODAY()+37</f>
-        <v>46028</v>
+        <v>46029</v>
       </c>
       <c r="F29" s="16">
         <v>15</v>
@@ -12541,7 +12501,7 @@
       <c r="D30" s="48"/>
       <c r="E30" s="46">
         <f ca="1">TODAY()+29</f>
-        <v>46020</v>
+        <v>46021</v>
       </c>
       <c r="F30" s="16">
         <v>5</v>
@@ -12781,7 +12741,7 @@
       <c r="D31" s="93"/>
       <c r="E31" s="46">
         <f ca="1">TODAY()+80</f>
-        <v>46071</v>
+        <v>46072</v>
       </c>
       <c r="F31" s="16">
         <v>5</v>
@@ -14109,7 +14069,7 @@
       </c>
       <c r="C5" s="51">
         <f ca="1">IFERROR(IF(MIN(Milestones[Start])=0,TODAY(),MIN(Milestones[Start])),TODAY())</f>
-        <v>45988</v>
+        <v>45989</v>
       </c>
       <c r="E5" s="67"/>
       <c r="H5" s="40"/>
@@ -14118,18 +14078,18 @@
       <c r="K5" s="41"/>
       <c r="L5" s="41"/>
       <c r="M5" s="42"/>
-      <c r="O5" s="107" t="s">
+      <c r="O5" s="109" t="s">
         <v>1</v>
       </c>
-      <c r="P5" s="107"/>
-      <c r="Q5" s="107"/>
-      <c r="R5" s="107"/>
-      <c r="S5" s="107"/>
-      <c r="T5" s="107"/>
-      <c r="U5" s="108">
+      <c r="P5" s="109"/>
+      <c r="Q5" s="109"/>
+      <c r="R5" s="109"/>
+      <c r="S5" s="109"/>
+      <c r="T5" s="109"/>
+      <c r="U5" s="110">
         <v>13</v>
       </c>
-      <c r="V5" s="108"/>
+      <c r="V5" s="110"/>
     </row>
     <row r="6" spans="1:63" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="10"/>
@@ -14175,7 +14135,7 @@
       <c r="AB6" s="27"/>
       <c r="AC6" s="27" t="str">
         <f ca="1">IF(OR(TEXT(AC7,"mmmm")=V6,TEXT(AC7,"mmmm")=O6,TEXT(AC7,"mmmm")=H6),"",TEXT(AC7,"mmmm"))</f>
-        <v/>
+        <v>January</v>
       </c>
       <c r="AD6" s="27"/>
       <c r="AE6" s="27"/>
@@ -14185,7 +14145,7 @@
       <c r="AI6" s="27"/>
       <c r="AJ6" s="81" t="str">
         <f ca="1">IF(OR(TEXT(AJ7,"mmmm")=AC6,TEXT(AJ7,"mmmm")=V6,TEXT(AJ7,"mmmm")=O6,TEXT(AJ7,"mmmm")=H6),"",TEXT(AJ7,"mmmm"))</f>
-        <v>January</v>
+        <v/>
       </c>
       <c r="AK6" s="81"/>
       <c r="AL6" s="81"/>
@@ -14229,227 +14189,227 @@
       <c r="B7" s="23"/>
       <c r="H7" s="58">
         <f ca="1">IFERROR(Project_Start+Scrolling_Increment,TODAY())</f>
-        <v>46001</v>
+        <v>46002</v>
       </c>
       <c r="I7" s="60">
         <f ca="1">H7+1</f>
-        <v>46002</v>
+        <v>46003</v>
       </c>
       <c r="J7" s="60">
         <f t="shared" ref="J7:AW7" ca="1" si="0">I7+1</f>
-        <v>46003</v>
+        <v>46004</v>
       </c>
       <c r="K7" s="60">
         <f ca="1">J7+1</f>
-        <v>46004</v>
+        <v>46005</v>
       </c>
       <c r="L7" s="60">
         <f t="shared" ca="1" si="0"/>
-        <v>46005</v>
+        <v>46006</v>
       </c>
       <c r="M7" s="60">
         <f t="shared" ca="1" si="0"/>
-        <v>46006</v>
+        <v>46007</v>
       </c>
       <c r="N7" s="60">
         <f t="shared" ca="1" si="0"/>
-        <v>46007</v>
+        <v>46008</v>
       </c>
       <c r="O7" s="60">
         <f ca="1">N7+1</f>
-        <v>46008</v>
+        <v>46009</v>
       </c>
       <c r="P7" s="60">
         <f ca="1">O7+1</f>
-        <v>46009</v>
+        <v>46010</v>
       </c>
       <c r="Q7" s="60">
         <f t="shared" ca="1" si="0"/>
-        <v>46010</v>
+        <v>46011</v>
       </c>
       <c r="R7" s="60">
         <f t="shared" ca="1" si="0"/>
-        <v>46011</v>
+        <v>46012</v>
       </c>
       <c r="S7" s="60">
         <f t="shared" ca="1" si="0"/>
-        <v>46012</v>
+        <v>46013</v>
       </c>
       <c r="T7" s="60">
         <f t="shared" ca="1" si="0"/>
-        <v>46013</v>
+        <v>46014</v>
       </c>
       <c r="U7" s="60">
         <f t="shared" ca="1" si="0"/>
-        <v>46014</v>
+        <v>46015</v>
       </c>
       <c r="V7" s="60">
         <f ca="1">U7+1</f>
-        <v>46015</v>
+        <v>46016</v>
       </c>
       <c r="W7" s="60">
         <f ca="1">V7+1</f>
-        <v>46016</v>
+        <v>46017</v>
       </c>
       <c r="X7" s="60">
         <f t="shared" ca="1" si="0"/>
-        <v>46017</v>
+        <v>46018</v>
       </c>
       <c r="Y7" s="60">
         <f t="shared" ca="1" si="0"/>
-        <v>46018</v>
+        <v>46019</v>
       </c>
       <c r="Z7" s="60">
         <f t="shared" ca="1" si="0"/>
-        <v>46019</v>
+        <v>46020</v>
       </c>
       <c r="AA7" s="60">
         <f t="shared" ca="1" si="0"/>
-        <v>46020</v>
+        <v>46021</v>
       </c>
       <c r="AB7" s="60">
         <f t="shared" ca="1" si="0"/>
-        <v>46021</v>
+        <v>46022</v>
       </c>
       <c r="AC7" s="60">
         <f ca="1">AB7+1</f>
-        <v>46022</v>
+        <v>46023</v>
       </c>
       <c r="AD7" s="60">
         <f ca="1">AC7+1</f>
-        <v>46023</v>
+        <v>46024</v>
       </c>
       <c r="AE7" s="60">
         <f t="shared" ca="1" si="0"/>
-        <v>46024</v>
+        <v>46025</v>
       </c>
       <c r="AF7" s="60">
         <f t="shared" ca="1" si="0"/>
-        <v>46025</v>
+        <v>46026</v>
       </c>
       <c r="AG7" s="60">
         <f t="shared" ca="1" si="0"/>
-        <v>46026</v>
+        <v>46027</v>
       </c>
       <c r="AH7" s="60">
         <f t="shared" ca="1" si="0"/>
-        <v>46027</v>
+        <v>46028</v>
       </c>
       <c r="AI7" s="60">
         <f t="shared" ca="1" si="0"/>
-        <v>46028</v>
+        <v>46029</v>
       </c>
       <c r="AJ7" s="60">
         <f ca="1">AI7+1</f>
-        <v>46029</v>
+        <v>46030</v>
       </c>
       <c r="AK7" s="60">
         <f ca="1">AJ7+1</f>
-        <v>46030</v>
+        <v>46031</v>
       </c>
       <c r="AL7" s="60">
         <f t="shared" ca="1" si="0"/>
-        <v>46031</v>
+        <v>46032</v>
       </c>
       <c r="AM7" s="60">
         <f t="shared" ca="1" si="0"/>
-        <v>46032</v>
+        <v>46033</v>
       </c>
       <c r="AN7" s="60">
         <f t="shared" ca="1" si="0"/>
-        <v>46033</v>
+        <v>46034</v>
       </c>
       <c r="AO7" s="60">
         <f t="shared" ca="1" si="0"/>
-        <v>46034</v>
+        <v>46035</v>
       </c>
       <c r="AP7" s="60">
         <f t="shared" ca="1" si="0"/>
-        <v>46035</v>
+        <v>46036</v>
       </c>
       <c r="AQ7" s="60">
         <f ca="1">AP7+1</f>
-        <v>46036</v>
+        <v>46037</v>
       </c>
       <c r="AR7" s="60">
         <f ca="1">AQ7+1</f>
-        <v>46037</v>
+        <v>46038</v>
       </c>
       <c r="AS7" s="60">
         <f t="shared" ca="1" si="0"/>
-        <v>46038</v>
+        <v>46039</v>
       </c>
       <c r="AT7" s="60">
         <f t="shared" ca="1" si="0"/>
-        <v>46039</v>
+        <v>46040</v>
       </c>
       <c r="AU7" s="60">
         <f t="shared" ca="1" si="0"/>
-        <v>46040</v>
+        <v>46041</v>
       </c>
       <c r="AV7" s="60">
         <f t="shared" ca="1" si="0"/>
-        <v>46041</v>
+        <v>46042</v>
       </c>
       <c r="AW7" s="60">
         <f t="shared" ca="1" si="0"/>
-        <v>46042</v>
+        <v>46043</v>
       </c>
       <c r="AX7" s="60">
         <f ca="1">AW7+1</f>
-        <v>46043</v>
+        <v>46044</v>
       </c>
       <c r="AY7" s="60">
         <f ca="1">AX7+1</f>
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="AZ7" s="60">
         <f t="shared" ref="AZ7:BD7" ca="1" si="1">AY7+1</f>
-        <v>46045</v>
+        <v>46046</v>
       </c>
       <c r="BA7" s="60">
         <f t="shared" ca="1" si="1"/>
-        <v>46046</v>
+        <v>46047</v>
       </c>
       <c r="BB7" s="60">
         <f t="shared" ca="1" si="1"/>
-        <v>46047</v>
+        <v>46048</v>
       </c>
       <c r="BC7" s="60">
         <f t="shared" ca="1" si="1"/>
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="BD7" s="60">
         <f t="shared" ca="1" si="1"/>
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="BE7" s="60">
         <f ca="1">BD7+1</f>
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="BF7" s="60">
         <f ca="1">BE7+1</f>
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="BG7" s="60">
         <f t="shared" ref="BG7:BK7" ca="1" si="2">BF7+1</f>
-        <v>46052</v>
+        <v>46053</v>
       </c>
       <c r="BH7" s="60">
         <f t="shared" ca="1" si="2"/>
-        <v>46053</v>
+        <v>46054</v>
       </c>
       <c r="BI7" s="60">
         <f t="shared" ca="1" si="2"/>
-        <v>46054</v>
+        <v>46055</v>
       </c>
       <c r="BJ7" s="60">
         <f t="shared" ca="1" si="2"/>
-        <v>46055</v>
+        <v>46056</v>
       </c>
       <c r="BK7" s="28">
         <f t="shared" ca="1" si="2"/>
-        <v>46056</v>
+        <v>46057</v>
       </c>
     </row>
     <row r="8" spans="1:63" ht="31.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -14472,15 +14432,15 @@
       <c r="G8" s="63"/>
       <c r="H8" s="62" t="str">
         <f ca="1">LEFT(TEXT(H7,"ddd"),1)</f>
-        <v>W</v>
+        <v>T</v>
       </c>
       <c r="I8" s="61" t="str">
         <f ca="1">LEFT(TEXT(I7,"ddd"),1)</f>
-        <v>T</v>
+        <v>F</v>
       </c>
       <c r="J8" s="61" t="str">
         <f ca="1">LEFT(TEXT(J7,"ddd"),1)</f>
-        <v>F</v>
+        <v>S</v>
       </c>
       <c r="K8" s="61" t="str">
         <f t="shared" ref="K8:AM8" ca="1" si="3">LEFT(TEXT(K7,"ddd"),1)</f>
@@ -14488,27 +14448,27 @@
       </c>
       <c r="L8" s="61" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>S</v>
+        <v>M</v>
       </c>
       <c r="M8" s="61" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>M</v>
+        <v>T</v>
       </c>
       <c r="N8" s="61" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>T</v>
+        <v>W</v>
       </c>
       <c r="O8" s="61" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>W</v>
+        <v>T</v>
       </c>
       <c r="P8" s="61" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>T</v>
+        <v>F</v>
       </c>
       <c r="Q8" s="61" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>F</v>
+        <v>S</v>
       </c>
       <c r="R8" s="61" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -14516,27 +14476,27 @@
       </c>
       <c r="S8" s="61" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>S</v>
+        <v>M</v>
       </c>
       <c r="T8" s="61" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>M</v>
+        <v>T</v>
       </c>
       <c r="U8" s="61" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>T</v>
+        <v>W</v>
       </c>
       <c r="V8" s="61" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>W</v>
+        <v>T</v>
       </c>
       <c r="W8" s="61" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>T</v>
+        <v>F</v>
       </c>
       <c r="X8" s="61" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>F</v>
+        <v>S</v>
       </c>
       <c r="Y8" s="61" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -14544,27 +14504,27 @@
       </c>
       <c r="Z8" s="61" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>S</v>
+        <v>M</v>
       </c>
       <c r="AA8" s="61" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>M</v>
+        <v>T</v>
       </c>
       <c r="AB8" s="61" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>T</v>
+        <v>W</v>
       </c>
       <c r="AC8" s="61" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>W</v>
+        <v>T</v>
       </c>
       <c r="AD8" s="61" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>T</v>
+        <v>F</v>
       </c>
       <c r="AE8" s="61" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>F</v>
+        <v>S</v>
       </c>
       <c r="AF8" s="61" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -14572,27 +14532,27 @@
       </c>
       <c r="AG8" s="61" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>S</v>
+        <v>M</v>
       </c>
       <c r="AH8" s="61" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>M</v>
+        <v>T</v>
       </c>
       <c r="AI8" s="61" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>T</v>
+        <v>W</v>
       </c>
       <c r="AJ8" s="61" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>W</v>
+        <v>T</v>
       </c>
       <c r="AK8" s="61" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>T</v>
+        <v>F</v>
       </c>
       <c r="AL8" s="61" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>F</v>
+        <v>S</v>
       </c>
       <c r="AM8" s="61" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -14600,27 +14560,27 @@
       </c>
       <c r="AN8" s="61" t="str">
         <f t="shared" ref="AN8:BK8" ca="1" si="4">LEFT(TEXT(AN7,"ddd"),1)</f>
-        <v>S</v>
+        <v>M</v>
       </c>
       <c r="AO8" s="61" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>M</v>
+        <v>T</v>
       </c>
       <c r="AP8" s="61" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>T</v>
+        <v>W</v>
       </c>
       <c r="AQ8" s="61" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>W</v>
+        <v>T</v>
       </c>
       <c r="AR8" s="61" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>T</v>
+        <v>F</v>
       </c>
       <c r="AS8" s="61" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>F</v>
+        <v>S</v>
       </c>
       <c r="AT8" s="61" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -14628,27 +14588,27 @@
       </c>
       <c r="AU8" s="61" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>S</v>
+        <v>M</v>
       </c>
       <c r="AV8" s="61" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>M</v>
+        <v>T</v>
       </c>
       <c r="AW8" s="61" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>T</v>
+        <v>W</v>
       </c>
       <c r="AX8" s="61" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>W</v>
+        <v>T</v>
       </c>
       <c r="AY8" s="61" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>T</v>
+        <v>F</v>
       </c>
       <c r="AZ8" s="61" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>F</v>
+        <v>S</v>
       </c>
       <c r="BA8" s="61" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -14656,27 +14616,27 @@
       </c>
       <c r="BB8" s="61" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>S</v>
+        <v>M</v>
       </c>
       <c r="BC8" s="61" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>M</v>
+        <v>T</v>
       </c>
       <c r="BD8" s="61" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>T</v>
+        <v>W</v>
       </c>
       <c r="BE8" s="61" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>W</v>
+        <v>T</v>
       </c>
       <c r="BF8" s="61" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>T</v>
+        <v>F</v>
       </c>
       <c r="BG8" s="61" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>F</v>
+        <v>S</v>
       </c>
       <c r="BH8" s="61" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -14684,15 +14644,15 @@
       </c>
       <c r="BI8" s="61" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>S</v>
+        <v>M</v>
       </c>
       <c r="BJ8" s="61" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>M</v>
+        <v>T</v>
       </c>
       <c r="BK8" s="59" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>T</v>
+        <v>W</v>
       </c>
     </row>
     <row r="9" spans="1:63" ht="30" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -15004,7 +14964,7 @@
       </c>
       <c r="E11" s="46">
         <f ca="1">TODAY()</f>
-        <v>45991</v>
+        <v>45992</v>
       </c>
       <c r="F11" s="16">
         <v>3</v>
@@ -15244,7 +15204,7 @@
       <c r="D12" s="47"/>
       <c r="E12" s="46">
         <f ca="1">TODAY()+5</f>
-        <v>45996</v>
+        <v>45997</v>
       </c>
       <c r="F12" s="16">
         <v>1</v>
@@ -15486,7 +15446,7 @@
       </c>
       <c r="E13" s="46">
         <f ca="1">TODAY()-3</f>
-        <v>45988</v>
+        <v>45989</v>
       </c>
       <c r="F13" s="16">
         <v>10</v>
@@ -15726,7 +15686,7 @@
       <c r="D14" s="47"/>
       <c r="E14" s="46">
         <f ca="1">TODAY()+20</f>
-        <v>46011</v>
+        <v>46012</v>
       </c>
       <c r="F14" s="16">
         <v>1</v>
@@ -15968,7 +15928,7 @@
       </c>
       <c r="E15" s="46">
         <f ca="1">TODAY()+6</f>
-        <v>45997</v>
+        <v>45998</v>
       </c>
       <c r="F15" s="16">
         <v>6</v>
@@ -16445,7 +16405,7 @@
       </c>
       <c r="E17" s="46">
         <f ca="1">TODAY()+6</f>
-        <v>45997</v>
+        <v>45998</v>
       </c>
       <c r="F17" s="16">
         <v>13</v>
@@ -16687,7 +16647,7 @@
       </c>
       <c r="E18" s="46">
         <f ca="1">TODAY()+7</f>
-        <v>45998</v>
+        <v>45999</v>
       </c>
       <c r="F18" s="16">
         <v>9</v>
@@ -16929,7 +16889,7 @@
       </c>
       <c r="E19" s="46">
         <f ca="1">TODAY()+15</f>
-        <v>46006</v>
+        <v>46007</v>
       </c>
       <c r="F19" s="16">
         <v>11</v>
@@ -17169,7 +17129,7 @@
       <c r="D20" s="47"/>
       <c r="E20" s="46">
         <f ca="1">TODAY()+24</f>
-        <v>46015</v>
+        <v>46016</v>
       </c>
       <c r="F20" s="16">
         <v>1</v>
@@ -17409,7 +17369,7 @@
       <c r="D21" s="47"/>
       <c r="E21" s="46">
         <f ca="1">TODAY()+25</f>
-        <v>46016</v>
+        <v>46017</v>
       </c>
       <c r="F21" s="16">
         <v>24</v>
@@ -17884,7 +17844,7 @@
       <c r="D23" s="47"/>
       <c r="E23" s="46">
         <f ca="1">TODAY()+15</f>
-        <v>46006</v>
+        <v>46007</v>
       </c>
       <c r="F23" s="16">
         <v>4</v>
@@ -18124,7 +18084,7 @@
       <c r="D24" s="47"/>
       <c r="E24" s="46">
         <f ca="1">TODAY()+19</f>
-        <v>46010</v>
+        <v>46011</v>
       </c>
       <c r="F24" s="16">
         <v>14</v>
@@ -18364,7 +18324,7 @@
       <c r="D25" s="47"/>
       <c r="E25" s="46">
         <f ca="1">TODAY()+35</f>
-        <v>46026</v>
+        <v>46027</v>
       </c>
       <c r="F25" s="16">
         <v>6</v>
@@ -18604,7 +18564,7 @@
       <c r="D26" s="47"/>
       <c r="E26" s="46">
         <f ca="1">TODAY()+48</f>
-        <v>46039</v>
+        <v>46040</v>
       </c>
       <c r="F26" s="16">
         <v>3</v>
@@ -18844,7 +18804,7 @@
       <c r="D27" s="47"/>
       <c r="E27" s="46">
         <f ca="1">TODAY()+40</f>
-        <v>46031</v>
+        <v>46032</v>
       </c>
       <c r="F27" s="16">
         <v>19</v>
@@ -19319,7 +19279,7 @@
       <c r="D29" s="47"/>
       <c r="E29" s="46">
         <f ca="1">TODAY()+37</f>
-        <v>46028</v>
+        <v>46029</v>
       </c>
       <c r="F29" s="16">
         <v>15</v>
@@ -19559,7 +19519,7 @@
       <c r="D30" s="47"/>
       <c r="E30" s="46">
         <f ca="1">TODAY()+29</f>
-        <v>46020</v>
+        <v>46021</v>
       </c>
       <c r="F30" s="16">
         <v>5</v>
@@ -19799,7 +19759,7 @@
       <c r="D31" s="47"/>
       <c r="E31" s="46">
         <f ca="1">TODAY()+80</f>
-        <v>46071</v>
+        <v>46072</v>
       </c>
       <c r="F31" s="16">
         <v>5</v>
@@ -20955,35 +20915,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <Image xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
-      <Url xsi:nil="true"/>
-      <Description xsi:nil="true"/>
-    </Image>
-    <Status xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">Not started</Status>
-    <Background xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">false</Background>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <ImageTagsTaxHTField xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </ImageTagsTaxHTField>
-    <TaxCatchAll xmlns="230e9df3-be65-4c73-a93b-d1236ebd677e" xsi:nil="true"/>
-    <MediaServiceKeyPoints xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010079F111ED35F8CC479449609E8A0923A6" ma:contentTypeVersion="26" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ac37c1753acd5e330d2062ccec26ea66">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xmlns:ns3="16c05727-aa75-4e4a-9b5f-8a80a1165891" xmlns:ns4="230e9df3-be65-4c73-a93b-d1236ebd677e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="3b340c7101c92c5120abd06486f94548" ns1:_="" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -21283,27 +21214,36 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{115E488A-90BD-4FEC-9F20-FFAF098D38E4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5"/>
-    <ds:schemaRef ds:uri="230e9df3-be65-4c73-a93b-d1236ebd677e"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FF8EE784-10F3-46EF-B6DC-D206373B3A17}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <Image xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
+      <Url xsi:nil="true"/>
+      <Description xsi:nil="true"/>
+    </Image>
+    <Status xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">Not started</Status>
+    <Background xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">false</Background>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <ImageTagsTaxHTField xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </ImageTagsTaxHTField>
+    <TaxCatchAll xmlns="230e9df3-be65-4c73-a93b-d1236ebd677e" xsi:nil="true"/>
+    <MediaServiceKeyPoints xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D999942B-3CC5-4007-B7B6-6870B5EC1C9B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -21324,6 +21264,26 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FF8EE784-10F3-46EF-B6DC-D206373B3A17}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{115E488A-90BD-4FEC-9F20-FFAF098D38E4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5"/>
+    <ds:schemaRef ds:uri="230e9df3-be65-4c73-a93b-d1236ebd677e"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata"/>
 </file>